--- a/output/casestudy_20260820.xlsx
+++ b/output/casestudy_20260820.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>4.636122200000045</v>
+        <v>4.982558300000164</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.835235399999874</v>
+        <v>4.904660000000149</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.537969099999827</v>
+        <v>5.425946499999554</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.836089699999775</v>
+        <v>5.049716699999408</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.759555699999964</v>
+        <v>5.150167600000714</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.711582899999939</v>
+        <v>5.262781699999323</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.6 초</t>
+          <t>5.0 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>4.9 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.5 초</t>
+          <t>5.4 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>5.0 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.8 초</t>
+          <t>5.2 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.7 초</t>
+          <t>5.3 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>29.4 초</t>
+          <t>31.8 초</t>
         </is>
       </c>
     </row>
